--- a/詳細設計書/タスク登録.xlsx
+++ b/詳細設計書/タスク登録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user34\Documents\project\TaskManager\詳細設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19C3D24-3147-482D-AF87-756BB6D42818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB11826-61AE-4C1E-A362-06EF999E8C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -324,58 +324,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>①タスク管理システムのタスク登録画面を立ち上げる
-②タスク登録画面でタスクの情報を入力する
-③入力が終わったら登録ボタンを押す
-④登録完了画面に遷移する</t>
-    <rPh sb="4" eb="6">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="14" eb="18">
-      <t>トウロクガメン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="29" eb="33">
-      <t>トウロクガメン</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>従業員のタスク情報をタスク管理システムに登録する</t>
     <rPh sb="0" eb="3">
       <t>ジュウギョウイン</t>
@@ -946,6 +894,129 @@
     </rPh>
     <rPh sb="20" eb="22">
       <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>①タスク管理システムのタスク登録画面を立ち上げる
+②タスク登録画面でタスク名を入力、カテゴリ情報を選択、期限の日時を指定、担当者名を選択、ステータスを選択、メモを入力(任意)する
+③入力が終わったら登録ボタンを押す
+④入力した情報が登録される
+   入力タスクID、登録日時、更新日時(登録時点では登録日時と同じ)は自動で登録される
+④登録完了画面に遷移する</t>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="29" eb="33">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="61" eb="64">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="105" eb="106">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="135" eb="137">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="138" eb="142">
+      <t>コウシンニチジ</t>
+    </rPh>
+    <rPh sb="143" eb="147">
+      <t>トウロクジテン</t>
+    </rPh>
+    <rPh sb="149" eb="153">
+      <t>トウロクニチジ</t>
+    </rPh>
+    <rPh sb="154" eb="155">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="158" eb="160">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="161" eb="163">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="168" eb="170">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="170" eb="172">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="172" eb="174">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="175" eb="177">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -3711,7 +3782,8 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" customWidth="1"/>
+    <col min="4" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="24.85546875" customWidth="1"/>
     <col min="11" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3806,7 +3878,7 @@
       <c r="B6" s="47"/>
       <c r="C6" s="48"/>
       <c r="D6" s="60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" s="47"/>
       <c r="F6" s="47"/>
@@ -3838,7 +3910,7 @@
       <c r="B8" s="47"/>
       <c r="C8" s="48"/>
       <c r="D8" s="62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" s="47"/>
       <c r="F8" s="47"/>
@@ -3847,7 +3919,7 @@
       <c r="I8" s="47"/>
       <c r="J8" s="61"/>
     </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+    <row r="9" spans="1:10" ht="89.25" customHeight="1">
       <c r="A9" s="76" t="s">
         <v>15</v>
       </c>
@@ -3856,7 +3928,7 @@
       </c>
       <c r="C9" s="48"/>
       <c r="D9" s="62" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -3872,7 +3944,7 @@
       </c>
       <c r="C10" s="48"/>
       <c r="D10" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10" s="47"/>
       <c r="F10" s="47"/>
@@ -3888,7 +3960,7 @@
       </c>
       <c r="C11" s="48"/>
       <c r="D11" s="62" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E11" s="47"/>
       <c r="F11" s="47"/>
@@ -3904,7 +3976,7 @@
       <c r="B12" s="47"/>
       <c r="C12" s="48"/>
       <c r="D12" s="62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E12" s="47"/>
       <c r="F12" s="47"/>
@@ -3920,7 +3992,7 @@
       <c r="B13" s="55"/>
       <c r="C13" s="64"/>
       <c r="D13" s="54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E13" s="55"/>
       <c r="F13" s="55"/>
@@ -7878,7 +7950,7 @@
       <c r="B5" s="58"/>
       <c r="C5" s="74"/>
       <c r="D5" s="103" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" s="58"/>
       <c r="F5" s="58"/>
@@ -8008,7 +8080,7 @@
       <c r="B15" s="47"/>
       <c r="C15" s="48"/>
       <c r="D15" s="60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E15" s="47"/>
       <c r="F15" s="47"/>
@@ -8018,7 +8090,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -8047,132 +8119,132 @@
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="47"/>
       <c r="C17" s="48"/>
       <c r="D17" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I17" s="47"/>
       <c r="J17" s="61"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="94" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="47"/>
       <c r="C18" s="48"/>
       <c r="D18" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I18" s="47"/>
       <c r="J18" s="61"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="94" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="48"/>
       <c r="D19" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="60" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I19" s="47"/>
       <c r="J19" s="61"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="94" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="48"/>
       <c r="D20" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="60" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I20" s="47"/>
       <c r="J20" s="61"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="94" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="47"/>
       <c r="C21" s="48"/>
       <c r="D21" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21" s="18"/>
       <c r="H21" s="60" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I21" s="47"/>
       <c r="J21" s="61"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="94" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" s="47"/>
       <c r="C22" s="48"/>
       <c r="D22" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G22" s="18"/>
       <c r="H22" s="60" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I22" s="47"/>
       <c r="J22" s="61"/>
@@ -8180,21 +8252,21 @@
     <row r="23" spans="1:10" ht="21" customHeight="1">
       <c r="A23" s="40"/>
       <c r="B23" s="45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C23" s="39"/>
       <c r="D23" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="38" t="s">
         <v>98</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>99</v>
       </c>
       <c r="F23" s="38"/>
       <c r="G23" s="38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H23" s="43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I23" s="41"/>
       <c r="J23" s="42"/>
@@ -8202,21 +8274,21 @@
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
       <c r="A24" s="40"/>
       <c r="B24" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C24" s="39"/>
       <c r="D24" s="38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F24" s="38"/>
       <c r="G24" s="38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H24" s="43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I24" s="41"/>
       <c r="J24" s="42"/>
@@ -8224,21 +8296,21 @@
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
       <c r="A25" s="40"/>
       <c r="B25" s="45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C25" s="44"/>
       <c r="D25" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F25" s="38"/>
       <c r="G25" s="38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H25" s="43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I25" s="41"/>
       <c r="J25" s="42"/>
@@ -9364,7 +9436,7 @@
       <c r="B5" s="58"/>
       <c r="C5" s="74"/>
       <c r="D5" s="103" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E5" s="58"/>
       <c r="F5" s="58"/>
@@ -9494,7 +9566,7 @@
       <c r="B15" s="47"/>
       <c r="C15" s="48"/>
       <c r="D15" s="60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E15" s="47"/>
       <c r="F15" s="47"/>
@@ -9504,7 +9576,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -9533,108 +9605,108 @@
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="47"/>
       <c r="C17" s="48"/>
       <c r="D17" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="18"/>
       <c r="H17" s="60" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I17" s="47"/>
       <c r="J17" s="61"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="94" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="47"/>
       <c r="C18" s="48"/>
       <c r="D18" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="18"/>
       <c r="H18" s="60" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I18" s="47"/>
       <c r="J18" s="61"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="94" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="48"/>
       <c r="D19" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="18"/>
       <c r="H19" s="60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I19" s="47"/>
       <c r="J19" s="61"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="94" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="48"/>
       <c r="D20" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="18"/>
       <c r="H20" s="60" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I20" s="47"/>
       <c r="J20" s="61"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="94" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="47"/>
       <c r="C21" s="48"/>
       <c r="D21" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="18"/>
       <c r="H21" s="60" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I21" s="47"/>
       <c r="J21" s="61"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="94" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" s="47"/>
       <c r="C22" s="48"/>
       <c r="D22" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="18"/>
       <c r="H22" s="60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I22" s="47"/>
       <c r="J22" s="61"/>
@@ -9642,21 +9714,21 @@
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="40"/>
       <c r="B23" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C23" s="39"/>
       <c r="D23" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F23" s="38"/>
       <c r="G23" s="38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H23" s="43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I23" s="41"/>
       <c r="J23" s="42"/>
@@ -10806,7 +10878,7 @@
       <c r="B5" s="58"/>
       <c r="C5" s="74"/>
       <c r="D5" s="103" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E5" s="58"/>
       <c r="F5" s="58"/>
@@ -10936,7 +11008,7 @@
       <c r="B15" s="47"/>
       <c r="C15" s="48"/>
       <c r="D15" s="60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E15" s="47"/>
       <c r="F15" s="47"/>
@@ -10946,7 +11018,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -10975,108 +11047,108 @@
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="47"/>
       <c r="C17" s="48"/>
       <c r="D17" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="18"/>
       <c r="H17" s="60" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I17" s="47"/>
       <c r="J17" s="61"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="94" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="47"/>
       <c r="C18" s="48"/>
       <c r="D18" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="18"/>
       <c r="H18" s="60" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I18" s="47"/>
       <c r="J18" s="61"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="94" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="48"/>
       <c r="D19" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="18"/>
       <c r="H19" s="60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I19" s="47"/>
       <c r="J19" s="61"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="94" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="48"/>
       <c r="D20" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="18"/>
       <c r="H20" s="60" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I20" s="47"/>
       <c r="J20" s="61"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="94" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="47"/>
       <c r="C21" s="48"/>
       <c r="D21" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="18"/>
       <c r="H21" s="60" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I21" s="47"/>
       <c r="J21" s="61"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="94" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" s="47"/>
       <c r="C22" s="48"/>
       <c r="D22" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="18"/>
       <c r="H22" s="60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I22" s="47"/>
       <c r="J22" s="61"/>
@@ -11084,21 +11156,21 @@
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="40"/>
       <c r="B23" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C23" s="39"/>
       <c r="D23" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F23" s="38"/>
       <c r="G23" s="38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H23" s="43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I23" s="41"/>
       <c r="J23" s="42"/>

--- a/詳細設計書/タスク登録.xlsx
+++ b/詳細設計書/タスク登録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user34\Documents\project\TaskManager\詳細設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB11826-61AE-4C1E-A362-06EF999E8C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C92C0F7-3674-4D67-BB62-845A7B653C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>

--- a/詳細設計書/タスク登録.xlsx
+++ b/詳細設計書/タスク登録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user34\Documents\project\TaskManager\詳細設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C92C0F7-3674-4D67-BB62-845A7B653C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94AFD32-1EF7-4CB2-954B-BDF7DC9CC2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -899,7 +899,7 @@
   </si>
   <si>
     <t>①タスク管理システムのタスク登録画面を立ち上げる
-②タスク登録画面でタスク名を入力、カテゴリ情報を選択、期限の日時を指定、担当者名を選択、ステータスを選択、メモを入力(任意)する
+②タスク登録画面でタスク名を入力、カテゴリ名を選択、期限の日時を指定、担当者名を選択、ステータスを選択、メモを入力(任意)する
 ③入力が終わったら登録ボタンを押す
 ④入力した情報が登録される
    入力タスクID、登録日時、更新日時(登録時点では登録日時と同じ)は自動で登録される
@@ -925,97 +925,97 @@
     <rPh sb="39" eb="41">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="46" eb="48">
+    <rPh sb="46" eb="47">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="112" eb="114">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="49" eb="51">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="55" eb="57">
+    <rPh sb="115" eb="117">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="134" eb="136">
       <t>ニチジ</t>
     </rPh>
-    <rPh sb="58" eb="60">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="61" eb="64">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="64" eb="65">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>ニンイ</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="94" eb="95">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
+    <rPh sb="137" eb="141">
+      <t>コウシンニチジ</t>
+    </rPh>
+    <rPh sb="142" eb="146">
+      <t>トウロクジテン</t>
+    </rPh>
+    <rPh sb="148" eb="152">
+      <t>トウロクニチジ</t>
+    </rPh>
+    <rPh sb="153" eb="154">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="160" eb="162">
       <t>トウロク</t>
     </rPh>
-    <rPh sb="105" eb="106">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="113" eb="115">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="116" eb="118">
+    <rPh sb="167" eb="169">
       <t>トウロク</t>
     </rPh>
-    <rPh sb="125" eb="127">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="133" eb="135">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="135" eb="137">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="138" eb="142">
-      <t>コウシンニチジ</t>
-    </rPh>
-    <rPh sb="143" eb="147">
-      <t>トウロクジテン</t>
-    </rPh>
-    <rPh sb="149" eb="153">
-      <t>トウロクニチジ</t>
-    </rPh>
-    <rPh sb="154" eb="155">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="158" eb="160">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="161" eb="163">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="168" eb="170">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="170" eb="172">
+    <rPh sb="169" eb="171">
       <t>カンリョウ</t>
     </rPh>
-    <rPh sb="172" eb="174">
+    <rPh sb="171" eb="173">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="175" eb="177">
+    <rPh sb="174" eb="176">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>

--- a/詳細設計書/タスク登録.xlsx
+++ b/詳細設計書/タスク登録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user34\Documents\project\TaskManager\詳細設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94AFD32-1EF7-4CB2-954B-BDF7DC9CC2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8940B5-E6F2-4D6E-A002-1945CE390903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="131">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -778,19 +778,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>メニュー画面にサーブレットを介して戻る</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>メニュー画面にサーブレットを介して遷移する</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -1028,7 +1015,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1097,6 +1084,27 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1112,7 +1120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="60">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -1803,11 +1811,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2185,6 +2271,36 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3928,7 +4044,7 @@
       </c>
       <c r="C9" s="48"/>
       <c r="D9" s="62" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -3960,7 +4076,7 @@
       </c>
       <c r="C11" s="48"/>
       <c r="D11" s="62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E11" s="47"/>
       <c r="F11" s="47"/>
@@ -3976,7 +4092,7 @@
       <c r="B12" s="47"/>
       <c r="C12" s="48"/>
       <c r="D12" s="62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E12" s="47"/>
       <c r="F12" s="47"/>
@@ -3992,7 +4108,7 @@
       <c r="B13" s="55"/>
       <c r="C13" s="64"/>
       <c r="D13" s="54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E13" s="55"/>
       <c r="F13" s="55"/>
@@ -7863,7 +7979,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1003"/>
+  <dimension ref="A1:J1002"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -8240,7 +8356,7 @@
         <v>77</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G22" s="18"/>
       <c r="H22" s="60" t="s">
@@ -8294,40 +8410,61 @@
       <c r="J24" s="42"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="40"/>
-      <c r="B25" s="45" t="s">
+      <c r="A25" s="100" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="126"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="127"/>
+    </row>
+    <row r="26" spans="1:10" ht="23.25" customHeight="1">
+      <c r="A26" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="47"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="131"/>
+      <c r="B27" s="128" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="38" t="s">
+      <c r="C27" s="132"/>
+      <c r="D27" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E27" s="129" t="s">
         <v>98</v>
       </c>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38" t="s">
+      <c r="F27" s="133"/>
+      <c r="G27" s="129" t="s">
         <v>103</v>
       </c>
-      <c r="H25" s="43" t="s">
+      <c r="H27" s="130" t="s">
         <v>125</v>
       </c>
-      <c r="I25" s="41"/>
-      <c r="J25" s="42"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A26" s="95"/>
-      <c r="B26" s="96"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="99"/>
-    </row>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="I27" s="134"/>
+      <c r="J27" s="135"/>
+    </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9303,9 +9440,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
     <row r="1001" ht="12.75" customHeight="1"/>
     <row r="1002" ht="12.75" customHeight="1"/>
-    <row r="1003" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:H26"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -9335,8 +9474,6 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9728,7 +9865,7 @@
         <v>103</v>
       </c>
       <c r="H23" s="43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I23" s="41"/>
       <c r="J23" s="42"/>
@@ -11170,7 +11307,7 @@
         <v>103</v>
       </c>
       <c r="H23" s="43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I23" s="41"/>
       <c r="J23" s="42"/>

--- a/詳細設計書/タスク登録.xlsx
+++ b/詳細設計書/タスク登録.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user34\Documents\project\TaskManager\詳細設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8940B5-E6F2-4D6E-A002-1945CE390903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AF3E77-8183-4C44-A205-AB2073ADAF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2389,16 +2389,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>62593</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>138793</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>971550</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>432707</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>81644</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2428,8 +2428,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="171450" y="1171575"/>
-          <a:ext cx="8515350" cy="4314826"/>
+          <a:off x="748393" y="2359479"/>
+          <a:ext cx="8523514" cy="4351565"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11293,7 +11293,7 @@
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="40"/>
       <c r="B23" s="45" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C23" s="39"/>
       <c r="D23" s="38" t="s">

--- a/詳細設計書/タスク登録.xlsx
+++ b/詳細設計書/タスク登録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user34\Documents\project\TaskManager\詳細設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AF3E77-8183-4C44-A205-AB2073ADAF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8E6C98-BCA8-42CD-9D39-B8F281409DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -2032,6 +2032,30 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2056,35 +2080,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2101,26 +2158,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2131,44 +2179,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2176,28 +2200,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2233,29 +2245,35 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2269,38 +2287,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2389,23 +2389,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>62593</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>138793</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>87992</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>432707</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>81644</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>334035</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>68037</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9D8940D-AD1A-B1EF-548A-DC708933FF05}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4037DC-5594-DB95-2ABA-674C462B2C85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2428,8 +2428,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="748393" y="2359479"/>
-          <a:ext cx="8523514" cy="4351565"/>
+          <a:off x="503465" y="1339849"/>
+          <a:ext cx="7545820" cy="4062188"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2737,85 +2737,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2835,46 +2835,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="58"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="46" t="s">
+      <c r="G13" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="48"/>
-      <c r="I13" s="46" t="s">
+      <c r="H13" s="56"/>
+      <c r="I13" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="47"/>
-      <c r="K13" s="48"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="56"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="46"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="48"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="56"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="46"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="48"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="56"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2883,13 +2883,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="49" t="s">
+      <c r="G17" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3904,19 +3904,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="86" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="86" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3928,194 +3928,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="87" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="87" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="91">
+      <c r="G2" s="65"/>
+      <c r="H2" s="70">
         <v>45919</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="57" t="s">
+      <c r="B5" s="91"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="59"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="60" t="s">
+      <c r="B6" s="55"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="61"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="80"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="60" t="s">
+      <c r="B7" s="55"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="99" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="61"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="80"/>
     </row>
     <row r="8" spans="1:10" ht="30.75" customHeight="1">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="62" t="s">
+      <c r="B8" s="55"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="61"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="80"/>
     </row>
     <row r="9" spans="1:10" ht="89.25" customHeight="1">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="62" t="s">
+      <c r="C9" s="56"/>
+      <c r="D9" s="79" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="61"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="80"/>
     </row>
     <row r="10" spans="1:10" ht="72" customHeight="1">
-      <c r="A10" s="77"/>
-      <c r="B10" s="79" t="s">
+      <c r="A10" s="93"/>
+      <c r="B10" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="62" t="s">
+      <c r="C10" s="56"/>
+      <c r="D10" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="61"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="80"/>
     </row>
     <row r="11" spans="1:10" ht="105.75" customHeight="1">
-      <c r="A11" s="78"/>
-      <c r="B11" s="79" t="s">
+      <c r="A11" s="94"/>
+      <c r="B11" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="62" t="s">
+      <c r="C11" s="56"/>
+      <c r="D11" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="61"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="80"/>
     </row>
     <row r="12" spans="1:10" ht="48" customHeight="1">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="62" t="s">
+      <c r="B12" s="55"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="61"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="80"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="54" t="s">
+      <c r="B13" s="82"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="95" t="s">
         <v>129</v>
       </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="56"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="96"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5106,17 +5106,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5125,14 +5122,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5151,19 +5151,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="86" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="86" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5175,48 +5175,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="87" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="87" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="91">
+      <c r="G2" s="65"/>
+      <c r="H2" s="70">
         <v>45919</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6572,19 +6572,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="86" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="86" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6596,48 +6596,48 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="93" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="87" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="91">
+      <c r="G2" s="65"/>
+      <c r="H2" s="70">
         <v>45918</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:13" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6667,7 +6667,6 @@
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -7992,19 +7991,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="86" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="86" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8016,192 +8015,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="87" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="87" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="91">
+      <c r="G2" s="65"/>
+      <c r="H2" s="70">
         <v>45919</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="68"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="103" t="s">
+      <c r="B5" s="91"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="107" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="59"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="61"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="80"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="104" t="e" vm="2">
+      <c r="A7" s="108" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="106"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="110"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="107"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="109"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="107"/>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="109"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="107"/>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="109"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="113"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="107"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="109"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="107"/>
-      <c r="B12" s="108"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="109"/>
+      <c r="A12" s="111"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="113"/>
     </row>
     <row r="13" spans="1:10" ht="114" customHeight="1">
-      <c r="A13" s="110"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="112"/>
+      <c r="A13" s="114"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="116"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="61"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="80"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="60" t="s">
+      <c r="B15" s="55"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="48"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="15" t="s">
         <v>28</v>
       </c>
@@ -8210,11 +8209,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="15" t="s">
         <v>30</v>
       </c>
@@ -8227,18 +8226,18 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="101" t="s">
+      <c r="H16" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="47"/>
-      <c r="J16" s="61"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="80"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="94" t="s">
+      <c r="A17" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="48"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="17" t="s">
         <v>79</v>
       </c>
@@ -8249,18 +8248,18 @@
         <v>94</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="60" t="s">
+      <c r="H17" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="I17" s="47"/>
-      <c r="J17" s="61"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="80"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="94" t="s">
+      <c r="A18" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="48"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="17" t="s">
         <v>80</v>
       </c>
@@ -8271,18 +8270,18 @@
         <v>91</v>
       </c>
       <c r="G18" s="18"/>
-      <c r="H18" s="60" t="s">
+      <c r="H18" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="47"/>
-      <c r="J18" s="61"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="80"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="94" t="s">
+      <c r="A19" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="48"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="17" t="s">
         <v>82</v>
       </c>
@@ -8293,18 +8292,18 @@
         <v>92</v>
       </c>
       <c r="G19" s="18"/>
-      <c r="H19" s="60" t="s">
+      <c r="H19" s="99" t="s">
         <v>109</v>
       </c>
-      <c r="I19" s="47"/>
-      <c r="J19" s="61"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="80"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="48"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="17" t="s">
         <v>84</v>
       </c>
@@ -8315,18 +8314,18 @@
         <v>95</v>
       </c>
       <c r="G20" s="18"/>
-      <c r="H20" s="60" t="s">
+      <c r="H20" s="99" t="s">
         <v>110</v>
       </c>
-      <c r="I20" s="47"/>
-      <c r="J20" s="61"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="80"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="94" t="s">
+      <c r="A21" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="17" t="s">
         <v>86</v>
       </c>
@@ -8337,18 +8336,18 @@
         <v>99</v>
       </c>
       <c r="G21" s="18"/>
-      <c r="H21" s="60" t="s">
+      <c r="H21" s="99" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="47"/>
-      <c r="J21" s="61"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="80"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="48"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="17" t="s">
         <v>88</v>
       </c>
@@ -8359,11 +8358,11 @@
         <v>126</v>
       </c>
       <c r="G22" s="18"/>
-      <c r="H22" s="60" t="s">
+      <c r="H22" s="99" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="47"/>
-      <c r="J22" s="61"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="80"/>
     </row>
     <row r="23" spans="1:10" ht="21" customHeight="1">
       <c r="A23" s="40"/>
@@ -8410,32 +8409,32 @@
       <c r="J24" s="42"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="100" t="s">
+      <c r="A25" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="126"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="126"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="126"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="127"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="104"/>
     </row>
     <row r="26" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A26" s="100" t="s">
+      <c r="A26" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="60" t="s">
+      <c r="B26" s="55"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="99" t="s">
         <v>122</v>
       </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="56"/>
       <c r="I26" s="15" t="s">
         <v>28</v>
       </c>
@@ -8444,26 +8443,26 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="131"/>
-      <c r="B27" s="128" t="s">
+      <c r="A27" s="49"/>
+      <c r="B27" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="132"/>
-      <c r="D27" s="129" t="s">
+      <c r="C27" s="50"/>
+      <c r="D27" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="E27" s="129" t="s">
+      <c r="E27" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="F27" s="133"/>
-      <c r="G27" s="129" t="s">
+      <c r="F27" s="51"/>
+      <c r="G27" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="H27" s="130" t="s">
+      <c r="H27" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="I27" s="134"/>
-      <c r="J27" s="135"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="53"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9442,16 +9441,11 @@
     <row r="1002" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -9459,11 +9453,16 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="A19:C19"/>
@@ -9499,19 +9498,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="86" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="86" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9523,192 +9522,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="87" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="87" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="91">
+      <c r="G2" s="65"/>
+      <c r="H2" s="70">
         <v>45919</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="68"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="103" t="s">
+      <c r="B5" s="91"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="107" t="s">
         <v>121</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="59"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="61"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="80"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="104" t="e" vm="3">
+      <c r="A7" s="108" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="106"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="110"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="107"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="109"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="107"/>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="109"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="107"/>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="109"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="113"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="107"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="109"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="107"/>
-      <c r="B12" s="108"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="109"/>
+      <c r="A12" s="111"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="113"/>
     </row>
     <row r="13" spans="1:10" ht="114" customHeight="1">
-      <c r="A13" s="110"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="112"/>
+      <c r="A13" s="114"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="116"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="61"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="80"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="60" t="s">
+      <c r="B15" s="55"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="99" t="s">
         <v>122</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="48"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="15" t="s">
         <v>28</v>
       </c>
@@ -9717,11 +9716,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="15" t="s">
         <v>30</v>
       </c>
@@ -9734,124 +9733,124 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="101" t="s">
+      <c r="H16" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="47"/>
-      <c r="J16" s="61"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="80"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="94" t="s">
+      <c r="A17" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="48"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="17" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="60" t="s">
+      <c r="H17" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="I17" s="47"/>
-      <c r="J17" s="61"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="80"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="94" t="s">
+      <c r="A18" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="48"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="17" t="s">
         <v>80</v>
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="60" t="s">
+      <c r="H18" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="I18" s="47"/>
-      <c r="J18" s="61"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="80"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="94" t="s">
+      <c r="A19" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="48"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="17" t="s">
         <v>82</v>
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="60" t="s">
+      <c r="H19" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="I19" s="47"/>
-      <c r="J19" s="61"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="80"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="48"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="17" t="s">
         <v>84</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="60" t="s">
+      <c r="H20" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="I20" s="47"/>
-      <c r="J20" s="61"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="80"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="94" t="s">
+      <c r="A21" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="17" t="s">
         <v>86</v>
       </c>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="60" t="s">
+      <c r="H21" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="I21" s="47"/>
-      <c r="J21" s="61"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="80"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="48"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="17" t="s">
         <v>88</v>
       </c>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="60" t="s">
+      <c r="H22" s="99" t="s">
         <v>119</v>
       </c>
-      <c r="I22" s="47"/>
-      <c r="J22" s="61"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="80"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="40"/>
       <c r="B23" s="45" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C23" s="39"/>
       <c r="D23" s="38" t="s">
@@ -9895,16 +9894,16 @@
       <c r="J25" s="42"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A26" s="95"/>
-      <c r="B26" s="96"/>
-      <c r="C26" s="97"/>
+      <c r="A26" s="120"/>
+      <c r="B26" s="121"/>
+      <c r="C26" s="122"/>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
       <c r="G26" s="19"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="99"/>
+      <c r="H26" s="95"/>
+      <c r="I26" s="118"/>
+      <c r="J26" s="119"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10885,25 +10884,6 @@
     <row r="1003" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="H18:J18"/>
@@ -10916,6 +10896,25 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10941,19 +10940,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="86" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="86" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -10965,192 +10964,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="87" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="87" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="91">
+      <c r="G2" s="65"/>
+      <c r="H2" s="70">
         <v>45919</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="68"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="103" t="s">
+      <c r="B5" s="91"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="59"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="61"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="80"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="104" t="e" vm="4">
+      <c r="A7" s="108" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="106"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="110"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="107"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="109"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="107"/>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="109"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="107"/>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="109"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="113"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="107"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="109"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="107"/>
-      <c r="B12" s="108"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="109"/>
+      <c r="A12" s="111"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="113"/>
     </row>
     <row r="13" spans="1:10" ht="114" customHeight="1">
-      <c r="A13" s="110"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="112"/>
+      <c r="A13" s="114"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="116"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="61"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="80"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="60" t="s">
+      <c r="B15" s="55"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="99" t="s">
         <v>122</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="48"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="15" t="s">
         <v>28</v>
       </c>
@@ -11159,11 +11158,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="15" t="s">
         <v>30</v>
       </c>
@@ -11176,119 +11175,119 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="101" t="s">
+      <c r="H16" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="47"/>
-      <c r="J16" s="61"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="80"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="94" t="s">
+      <c r="A17" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="48"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="17" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="60" t="s">
+      <c r="H17" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="I17" s="47"/>
-      <c r="J17" s="61"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="80"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="94" t="s">
+      <c r="A18" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="48"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="17" t="s">
         <v>80</v>
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="60" t="s">
+      <c r="H18" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="I18" s="47"/>
-      <c r="J18" s="61"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="80"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="94" t="s">
+      <c r="A19" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="48"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="17" t="s">
         <v>82</v>
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="60" t="s">
+      <c r="H19" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="I19" s="47"/>
-      <c r="J19" s="61"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="80"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="48"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="17" t="s">
         <v>84</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="60" t="s">
+      <c r="H20" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="I20" s="47"/>
-      <c r="J20" s="61"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="80"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="94" t="s">
+      <c r="A21" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="17" t="s">
         <v>86</v>
       </c>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="60" t="s">
+      <c r="H21" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="I21" s="47"/>
-      <c r="J21" s="61"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="80"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="48"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="17" t="s">
         <v>88</v>
       </c>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="60" t="s">
+      <c r="H22" s="99" t="s">
         <v>119</v>
       </c>
-      <c r="I22" s="47"/>
-      <c r="J22" s="61"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="80"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="40"/>
@@ -11337,16 +11336,16 @@
       <c r="J25" s="42"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A26" s="95"/>
-      <c r="B26" s="96"/>
-      <c r="C26" s="97"/>
+      <c r="A26" s="120"/>
+      <c r="B26" s="121"/>
+      <c r="C26" s="122"/>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
       <c r="G26" s="19"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="99"/>
+      <c r="H26" s="95"/>
+      <c r="I26" s="118"/>
+      <c r="J26" s="119"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12327,6 +12326,21 @@
     <row r="1003" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -12343,21 +12357,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12376,182 +12375,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="86" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="86" t="s">
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="86" t="s">
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="86" t="s">
+      <c r="P1" s="63"/>
+      <c r="Q1" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="74"/>
-      <c r="S1" s="86" t="s">
+      <c r="R1" s="63"/>
+      <c r="S1" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="59"/>
+      <c r="T1" s="98"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="87"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="87"/>
-      <c r="T2" s="122"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="128"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="123"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="129"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="90"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="90"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="90"/>
-      <c r="T4" s="124"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="68"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="68"/>
+      <c r="T4" s="130"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="106" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="57" t="s">
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="59"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="91"/>
+      <c r="P5" s="91"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="91"/>
+      <c r="S5" s="91"/>
+      <c r="T5" s="98"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="60" t="s">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="61"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="55"/>
+      <c r="Q6" s="55"/>
+      <c r="R6" s="55"/>
+      <c r="S6" s="55"/>
+      <c r="T6" s="80"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="60" t="s">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="61"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="55"/>
+      <c r="Q7" s="55"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="80"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12750,37 +12749,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="120" t="s">
+      <c r="B15" s="56"/>
+      <c r="C15" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="48"/>
-      <c r="E15" s="101" t="s">
+      <c r="D15" s="56"/>
+      <c r="E15" s="117" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="101" t="s">
+      <c r="F15" s="56"/>
+      <c r="G15" s="117" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="47"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="101" t="s">
+      <c r="H15" s="55"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="117" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="48"/>
-      <c r="L15" s="101" t="s">
+      <c r="K15" s="56"/>
+      <c r="L15" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="47"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="101" t="s">
+      <c r="M15" s="55"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="117" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="48"/>
+      <c r="P15" s="55"/>
+      <c r="Q15" s="56"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -12792,37 +12791,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="113">
+      <c r="A16" s="131">
         <v>1</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="114" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="48"/>
-      <c r="E16" s="114" t="s">
+      <c r="D16" s="56"/>
+      <c r="E16" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="119" t="s">
+      <c r="F16" s="56"/>
+      <c r="G16" s="123" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="47"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="119" t="s">
+      <c r="H16" s="55"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="48"/>
-      <c r="L16" s="117" t="s">
+      <c r="K16" s="56"/>
+      <c r="L16" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="47"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="117" t="s">
+      <c r="M16" s="55"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="48"/>
+      <c r="P16" s="55"/>
+      <c r="Q16" s="56"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12834,37 +12833,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="113">
+      <c r="A17" s="131">
         <v>2</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="114" t="s">
+      <c r="B17" s="56"/>
+      <c r="C17" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="48"/>
-      <c r="E17" s="114" t="s">
+      <c r="D17" s="56"/>
+      <c r="E17" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="119" t="s">
+      <c r="F17" s="56"/>
+      <c r="G17" s="123" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="119" t="s">
+      <c r="H17" s="55"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="48"/>
-      <c r="L17" s="117" t="s">
+      <c r="K17" s="56"/>
+      <c r="L17" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="47"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="117" t="s">
+      <c r="M17" s="55"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="48"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="56"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12876,23 +12875,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="113"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="119"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="117"/>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="48"/>
+      <c r="A18" s="131"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="125"/>
+      <c r="M18" s="55"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="125"/>
+      <c r="P18" s="55"/>
+      <c r="Q18" s="56"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12904,23 +12903,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="113"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="117"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="48"/>
+      <c r="A19" s="131"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="125"/>
+      <c r="M19" s="55"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="125"/>
+      <c r="P19" s="55"/>
+      <c r="Q19" s="56"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12932,23 +12931,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="113"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="114"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="119"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="119"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="117"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="117"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="48"/>
+      <c r="A20" s="131"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="132"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="125"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="56"/>
+      <c r="O20" s="125"/>
+      <c r="P20" s="55"/>
+      <c r="Q20" s="56"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12960,23 +12959,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="113"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="119"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="119"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="117"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="117"/>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="48"/>
+      <c r="A21" s="131"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="125"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="125"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="56"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12988,23 +12987,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="113"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="114"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="119"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="117"/>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="48"/>
+      <c r="A22" s="131"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="132"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="123"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="125"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="125"/>
+      <c r="P22" s="55"/>
+      <c r="Q22" s="56"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13016,23 +13015,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="113"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="114"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="114"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="117"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="117"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="48"/>
+      <c r="A23" s="131"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="125"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="125"/>
+      <c r="P23" s="55"/>
+      <c r="Q23" s="56"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13044,23 +13043,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="113"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="114"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="114"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="117"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="117"/>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="48"/>
+      <c r="A24" s="131"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="132"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="123"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="125"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="125"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="56"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13072,23 +13071,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="113"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="114"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="114"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="117"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="117"/>
-      <c r="P25" s="47"/>
-      <c r="Q25" s="48"/>
+      <c r="A25" s="131"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="132"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="123"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="125"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="56"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13100,23 +13099,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="113"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="114"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="114"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="119"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="117"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="117"/>
-      <c r="P26" s="47"/>
-      <c r="Q26" s="48"/>
+      <c r="A26" s="131"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="123"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="125"/>
+      <c r="M26" s="55"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="125"/>
+      <c r="P26" s="55"/>
+      <c r="Q26" s="56"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13128,23 +13127,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="113"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="114"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="117"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="117"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="48"/>
+      <c r="A27" s="131"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="132"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="123"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="123"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="125"/>
+      <c r="M27" s="55"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="125"/>
+      <c r="P27" s="55"/>
+      <c r="Q27" s="56"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13156,23 +13155,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="113"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="114"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="119"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="117"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="117"/>
-      <c r="P28" s="47"/>
-      <c r="Q28" s="48"/>
+      <c r="A28" s="131"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="123"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="123"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="125"/>
+      <c r="M28" s="55"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="125"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="56"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13184,23 +13183,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="113"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="114"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="119"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="117"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="117"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="48"/>
+      <c r="A29" s="131"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="132"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="123"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="123"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="125"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="125"/>
+      <c r="P29" s="55"/>
+      <c r="Q29" s="56"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13212,23 +13211,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="113"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="117"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="117"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="48"/>
+      <c r="A30" s="131"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="132"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="123"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="123"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="125"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="125"/>
+      <c r="P30" s="55"/>
+      <c r="Q30" s="56"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13240,23 +13239,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="115"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="116"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="125"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="125"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="118"/>
-      <c r="M31" s="55"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="118"/>
-      <c r="P31" s="55"/>
-      <c r="Q31" s="64"/>
+      <c r="A31" s="134"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="124"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="124"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="126"/>
+      <c r="M31" s="82"/>
+      <c r="N31" s="83"/>
+      <c r="O31" s="126"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="83"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14254,62 +14253,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14334,62 +14333,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/詳細設計書/タスク登録.xlsx
+++ b/詳細設計書/タスク登録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user34\Documents\project\TaskManager\詳細設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8E6C98-BCA8-42CD-9D39-B8F281409DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE3C430-E0A1-489D-84BE-2085DF26DAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -2080,68 +2080,35 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2158,17 +2125,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2179,20 +2155,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2203,20 +2203,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2245,7 +2233,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2263,17 +2263,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2287,20 +2299,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2389,23 +2389,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>87992</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>306455</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>107673</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>334035</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>68037</xdr:rowOff>
+      <xdr:colOff>1039316</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>24847</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="17" name="図 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4037DC-5594-DB95-2ABA-674C462B2C85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8910B31-E45A-27A0-98C7-5F16F8280D63}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2428,8 +2428,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="503465" y="1339849"/>
-          <a:ext cx="7545820" cy="4062188"/>
+          <a:off x="1325216" y="1200977"/>
+          <a:ext cx="7441774" cy="4058479"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3904,19 +3904,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="62" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="62" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="82"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3928,72 +3928,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="58"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="70">
+      <c r="G2" s="96"/>
+      <c r="H2" s="99">
         <v>45919</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="58"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="97" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="98"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="67"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="83" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="55"/>
       <c r="C6" s="56"/>
-      <c r="D6" s="99" t="s">
+      <c r="D6" s="68" t="s">
         <v>72</v>
       </c>
       <c r="E6" s="55"/>
@@ -4001,15 +4001,15 @@
       <c r="G6" s="55"/>
       <c r="H6" s="55"/>
       <c r="I6" s="55"/>
-      <c r="J6" s="80"/>
+      <c r="J6" s="69"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="83" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="55"/>
       <c r="C7" s="56"/>
-      <c r="D7" s="99" t="s">
+      <c r="D7" s="68" t="s">
         <v>71</v>
       </c>
       <c r="E7" s="55"/>
@@ -4017,15 +4017,15 @@
       <c r="G7" s="55"/>
       <c r="H7" s="55"/>
       <c r="I7" s="55"/>
-      <c r="J7" s="80"/>
+      <c r="J7" s="69"/>
     </row>
     <row r="8" spans="1:10" ht="30.75" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="83" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="55"/>
       <c r="C8" s="56"/>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="70" t="s">
         <v>73</v>
       </c>
       <c r="E8" s="55"/>
@@ -4033,17 +4033,17 @@
       <c r="G8" s="55"/>
       <c r="H8" s="55"/>
       <c r="I8" s="55"/>
-      <c r="J8" s="80"/>
+      <c r="J8" s="69"/>
     </row>
     <row r="9" spans="1:10" ht="89.25" customHeight="1">
-      <c r="A9" s="92" t="s">
+      <c r="A9" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="87" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="56"/>
-      <c r="D9" s="79" t="s">
+      <c r="D9" s="70" t="s">
         <v>130</v>
       </c>
       <c r="E9" s="55"/>
@@ -4051,15 +4051,15 @@
       <c r="G9" s="55"/>
       <c r="H9" s="55"/>
       <c r="I9" s="55"/>
-      <c r="J9" s="80"/>
+      <c r="J9" s="69"/>
     </row>
     <row r="10" spans="1:10" ht="72" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="77" t="s">
+      <c r="A10" s="85"/>
+      <c r="B10" s="87" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="56"/>
-      <c r="D10" s="79" t="s">
+      <c r="D10" s="70" t="s">
         <v>93</v>
       </c>
       <c r="E10" s="55"/>
@@ -4067,15 +4067,15 @@
       <c r="G10" s="55"/>
       <c r="H10" s="55"/>
       <c r="I10" s="55"/>
-      <c r="J10" s="80"/>
+      <c r="J10" s="69"/>
     </row>
     <row r="11" spans="1:10" ht="105.75" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="77" t="s">
+      <c r="A11" s="86"/>
+      <c r="B11" s="87" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="56"/>
-      <c r="D11" s="79" t="s">
+      <c r="D11" s="70" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="55"/>
@@ -4083,15 +4083,15 @@
       <c r="G11" s="55"/>
       <c r="H11" s="55"/>
       <c r="I11" s="55"/>
-      <c r="J11" s="80"/>
+      <c r="J11" s="69"/>
     </row>
     <row r="12" spans="1:10" ht="48" customHeight="1">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="83" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="55"/>
       <c r="C12" s="56"/>
-      <c r="D12" s="79" t="s">
+      <c r="D12" s="70" t="s">
         <v>127</v>
       </c>
       <c r="E12" s="55"/>
@@ -4099,23 +4099,23 @@
       <c r="G12" s="55"/>
       <c r="H12" s="55"/>
       <c r="I12" s="55"/>
-      <c r="J12" s="80"/>
+      <c r="J12" s="69"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="82"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="95" t="s">
+      <c r="B13" s="63"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="96"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="64"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5106,6 +5106,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5114,25 +5133,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5154,16 +5154,16 @@
       <c r="A1" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="62" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="62" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="82"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5175,48 +5175,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="58"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="70">
+      <c r="G2" s="96"/>
+      <c r="H2" s="99">
         <v>45919</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="58"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6575,16 +6575,16 @@
       <c r="A1" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="62" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="62" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="82"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6596,48 +6596,48 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="58"/>
-      <c r="C2" s="67"/>
+      <c r="C2" s="77"/>
       <c r="D2" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="70">
+      <c r="G2" s="96"/>
+      <c r="H2" s="99">
         <v>45918</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="58"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:13" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7994,16 +7994,16 @@
       <c r="A1" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="62" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="62" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="82"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8015,64 +8015,64 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="58"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="70">
+      <c r="G2" s="96"/>
+      <c r="H2" s="99">
         <v>45919</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="58"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="87"/>
+      <c r="A4" s="76"/>
       <c r="B4" s="58"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="75"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="107" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="114" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="98"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="67"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="102" t="s">
@@ -8086,93 +8086,93 @@
       <c r="G6" s="55"/>
       <c r="H6" s="55"/>
       <c r="I6" s="55"/>
-      <c r="J6" s="80"/>
+      <c r="J6" s="69"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="108" t="e" vm="2">
+      <c r="A7" s="104" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="111"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="113"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="109"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="111"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
+      <c r="A9" s="107"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="109"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="113"/>
+      <c r="A10" s="107"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="109"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="111"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
+      <c r="A11" s="107"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="111"/>
-      <c r="B12" s="112"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="112"/>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="113"/>
+      <c r="A12" s="107"/>
+      <c r="B12" s="108"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="109"/>
     </row>
     <row r="13" spans="1:10" ht="114" customHeight="1">
-      <c r="A13" s="114"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="116"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="112"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="102" t="s">
@@ -8186,7 +8186,7 @@
       <c r="G14" s="55"/>
       <c r="H14" s="55"/>
       <c r="I14" s="55"/>
-      <c r="J14" s="80"/>
+      <c r="J14" s="69"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="102" t="s">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="B15" s="55"/>
       <c r="C15" s="56"/>
-      <c r="D15" s="99" t="s">
+      <c r="D15" s="68" t="s">
         <v>123</v>
       </c>
       <c r="E15" s="55"/>
@@ -8226,14 +8226,14 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="117" t="s">
+      <c r="H16" s="103" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="55"/>
-      <c r="J16" s="80"/>
+      <c r="J16" s="69"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="105" t="s">
+      <c r="A17" s="117" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="55"/>
@@ -8248,14 +8248,14 @@
         <v>94</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="99" t="s">
+      <c r="H17" s="68" t="s">
         <v>107</v>
       </c>
       <c r="I17" s="55"/>
-      <c r="J17" s="80"/>
+      <c r="J17" s="69"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="117" t="s">
         <v>75</v>
       </c>
       <c r="B18" s="55"/>
@@ -8270,14 +8270,14 @@
         <v>91</v>
       </c>
       <c r="G18" s="18"/>
-      <c r="H18" s="99" t="s">
+      <c r="H18" s="68" t="s">
         <v>108</v>
       </c>
       <c r="I18" s="55"/>
-      <c r="J18" s="80"/>
+      <c r="J18" s="69"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="105" t="s">
+      <c r="A19" s="117" t="s">
         <v>81</v>
       </c>
       <c r="B19" s="55"/>
@@ -8292,14 +8292,14 @@
         <v>92</v>
       </c>
       <c r="G19" s="18"/>
-      <c r="H19" s="99" t="s">
+      <c r="H19" s="68" t="s">
         <v>109</v>
       </c>
       <c r="I19" s="55"/>
-      <c r="J19" s="80"/>
+      <c r="J19" s="69"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="105" t="s">
+      <c r="A20" s="117" t="s">
         <v>83</v>
       </c>
       <c r="B20" s="55"/>
@@ -8314,14 +8314,14 @@
         <v>95</v>
       </c>
       <c r="G20" s="18"/>
-      <c r="H20" s="99" t="s">
+      <c r="H20" s="68" t="s">
         <v>110</v>
       </c>
       <c r="I20" s="55"/>
-      <c r="J20" s="80"/>
+      <c r="J20" s="69"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="105" t="s">
+      <c r="A21" s="117" t="s">
         <v>85</v>
       </c>
       <c r="B21" s="55"/>
@@ -8336,14 +8336,14 @@
         <v>99</v>
       </c>
       <c r="G21" s="18"/>
-      <c r="H21" s="99" t="s">
+      <c r="H21" s="68" t="s">
         <v>111</v>
       </c>
       <c r="I21" s="55"/>
-      <c r="J21" s="80"/>
+      <c r="J21" s="69"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="117" t="s">
         <v>87</v>
       </c>
       <c r="B22" s="55"/>
@@ -8358,11 +8358,11 @@
         <v>126</v>
       </c>
       <c r="G22" s="18"/>
-      <c r="H22" s="99" t="s">
+      <c r="H22" s="68" t="s">
         <v>112</v>
       </c>
       <c r="I22" s="55"/>
-      <c r="J22" s="80"/>
+      <c r="J22" s="69"/>
     </row>
     <row r="23" spans="1:10" ht="21" customHeight="1">
       <c r="A23" s="40"/>
@@ -8412,15 +8412,15 @@
       <c r="A25" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="104"/>
+      <c r="B25" s="115"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="115"/>
+      <c r="G25" s="115"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="116"/>
     </row>
     <row r="26" spans="1:10" ht="23.25" customHeight="1">
       <c r="A26" s="102" t="s">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="B26" s="55"/>
       <c r="C26" s="56"/>
-      <c r="D26" s="99" t="s">
+      <c r="D26" s="68" t="s">
         <v>122</v>
       </c>
       <c r="E26" s="55"/>
@@ -9441,23 +9441,6 @@
     <row r="1002" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D26:H26"/>
@@ -9473,6 +9456,23 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9501,16 +9501,16 @@
       <c r="A1" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="62" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="62" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="82"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9522,64 +9522,64 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="58"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="70">
+      <c r="G2" s="96"/>
+      <c r="H2" s="99">
         <v>45919</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="58"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="87"/>
+      <c r="A4" s="76"/>
       <c r="B4" s="58"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="75"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="107" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="114" t="s">
         <v>121</v>
       </c>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="98"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="67"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="102" t="s">
@@ -9593,93 +9593,93 @@
       <c r="G6" s="55"/>
       <c r="H6" s="55"/>
       <c r="I6" s="55"/>
-      <c r="J6" s="80"/>
+      <c r="J6" s="69"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="108" t="e" vm="3">
+      <c r="A7" s="104" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="111"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="113"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="109"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="111"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
+      <c r="A9" s="107"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="109"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="113"/>
+      <c r="A10" s="107"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="109"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="111"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
+      <c r="A11" s="107"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="111"/>
-      <c r="B12" s="112"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="112"/>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="113"/>
+      <c r="A12" s="107"/>
+      <c r="B12" s="108"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="109"/>
     </row>
     <row r="13" spans="1:10" ht="114" customHeight="1">
-      <c r="A13" s="114"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="116"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="112"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="102" t="s">
@@ -9693,7 +9693,7 @@
       <c r="G14" s="55"/>
       <c r="H14" s="55"/>
       <c r="I14" s="55"/>
-      <c r="J14" s="80"/>
+      <c r="J14" s="69"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="102" t="s">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="B15" s="55"/>
       <c r="C15" s="56"/>
-      <c r="D15" s="99" t="s">
+      <c r="D15" s="68" t="s">
         <v>122</v>
       </c>
       <c r="E15" s="55"/>
@@ -9733,14 +9733,14 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="117" t="s">
+      <c r="H16" s="103" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="55"/>
-      <c r="J16" s="80"/>
+      <c r="J16" s="69"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="105" t="s">
+      <c r="A17" s="117" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="55"/>
@@ -9751,14 +9751,14 @@
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="99" t="s">
+      <c r="H17" s="68" t="s">
         <v>114</v>
       </c>
       <c r="I17" s="55"/>
-      <c r="J17" s="80"/>
+      <c r="J17" s="69"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="117" t="s">
         <v>75</v>
       </c>
       <c r="B18" s="55"/>
@@ -9769,14 +9769,14 @@
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="99" t="s">
+      <c r="H18" s="68" t="s">
         <v>115</v>
       </c>
       <c r="I18" s="55"/>
-      <c r="J18" s="80"/>
+      <c r="J18" s="69"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="105" t="s">
+      <c r="A19" s="117" t="s">
         <v>81</v>
       </c>
       <c r="B19" s="55"/>
@@ -9787,14 +9787,14 @@
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="99" t="s">
+      <c r="H19" s="68" t="s">
         <v>116</v>
       </c>
       <c r="I19" s="55"/>
-      <c r="J19" s="80"/>
+      <c r="J19" s="69"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="105" t="s">
+      <c r="A20" s="117" t="s">
         <v>83</v>
       </c>
       <c r="B20" s="55"/>
@@ -9805,14 +9805,14 @@
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="99" t="s">
+      <c r="H20" s="68" t="s">
         <v>117</v>
       </c>
       <c r="I20" s="55"/>
-      <c r="J20" s="80"/>
+      <c r="J20" s="69"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="105" t="s">
+      <c r="A21" s="117" t="s">
         <v>85</v>
       </c>
       <c r="B21" s="55"/>
@@ -9823,14 +9823,14 @@
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="99" t="s">
+      <c r="H21" s="68" t="s">
         <v>118</v>
       </c>
       <c r="I21" s="55"/>
-      <c r="J21" s="80"/>
+      <c r="J21" s="69"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="117" t="s">
         <v>87</v>
       </c>
       <c r="B22" s="55"/>
@@ -9841,11 +9841,11 @@
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="99" t="s">
+      <c r="H22" s="68" t="s">
         <v>119</v>
       </c>
       <c r="I22" s="55"/>
-      <c r="J22" s="80"/>
+      <c r="J22" s="69"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="40"/>
@@ -9901,7 +9901,7 @@
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
       <c r="G26" s="19"/>
-      <c r="H26" s="95"/>
+      <c r="H26" s="62"/>
       <c r="I26" s="118"/>
       <c r="J26" s="119"/>
     </row>
@@ -10884,6 +10884,25 @@
     <row r="1003" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="H18:J18"/>
@@ -10896,25 +10915,6 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10943,16 +10943,16 @@
       <c r="A1" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="62" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="62" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="82"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -10964,64 +10964,64 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="58"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="70">
+      <c r="G2" s="96"/>
+      <c r="H2" s="99">
         <v>45919</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="58"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="87"/>
+      <c r="A4" s="76"/>
       <c r="B4" s="58"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="75"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="107" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="114" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="98"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="67"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="102" t="s">
@@ -11035,93 +11035,93 @@
       <c r="G6" s="55"/>
       <c r="H6" s="55"/>
       <c r="I6" s="55"/>
-      <c r="J6" s="80"/>
+      <c r="J6" s="69"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="108" t="e" vm="4">
+      <c r="A7" s="104" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="111"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="113"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="109"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="111"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
+      <c r="A9" s="107"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="109"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="113"/>
+      <c r="A10" s="107"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="109"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="111"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
+      <c r="A11" s="107"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="111"/>
-      <c r="B12" s="112"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="112"/>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="113"/>
+      <c r="A12" s="107"/>
+      <c r="B12" s="108"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="109"/>
     </row>
     <row r="13" spans="1:10" ht="114" customHeight="1">
-      <c r="A13" s="114"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="116"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="112"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="102" t="s">
@@ -11135,7 +11135,7 @@
       <c r="G14" s="55"/>
       <c r="H14" s="55"/>
       <c r="I14" s="55"/>
-      <c r="J14" s="80"/>
+      <c r="J14" s="69"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="102" t="s">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="B15" s="55"/>
       <c r="C15" s="56"/>
-      <c r="D15" s="99" t="s">
+      <c r="D15" s="68" t="s">
         <v>122</v>
       </c>
       <c r="E15" s="55"/>
@@ -11175,14 +11175,14 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="117" t="s">
+      <c r="H16" s="103" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="55"/>
-      <c r="J16" s="80"/>
+      <c r="J16" s="69"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="105" t="s">
+      <c r="A17" s="117" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="55"/>
@@ -11193,14 +11193,14 @@
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="99" t="s">
+      <c r="H17" s="68" t="s">
         <v>114</v>
       </c>
       <c r="I17" s="55"/>
-      <c r="J17" s="80"/>
+      <c r="J17" s="69"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="117" t="s">
         <v>75</v>
       </c>
       <c r="B18" s="55"/>
@@ -11211,14 +11211,14 @@
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="99" t="s">
+      <c r="H18" s="68" t="s">
         <v>115</v>
       </c>
       <c r="I18" s="55"/>
-      <c r="J18" s="80"/>
+      <c r="J18" s="69"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="105" t="s">
+      <c r="A19" s="117" t="s">
         <v>81</v>
       </c>
       <c r="B19" s="55"/>
@@ -11229,14 +11229,14 @@
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="99" t="s">
+      <c r="H19" s="68" t="s">
         <v>116</v>
       </c>
       <c r="I19" s="55"/>
-      <c r="J19" s="80"/>
+      <c r="J19" s="69"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="105" t="s">
+      <c r="A20" s="117" t="s">
         <v>83</v>
       </c>
       <c r="B20" s="55"/>
@@ -11247,14 +11247,14 @@
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="99" t="s">
+      <c r="H20" s="68" t="s">
         <v>117</v>
       </c>
       <c r="I20" s="55"/>
-      <c r="J20" s="80"/>
+      <c r="J20" s="69"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="105" t="s">
+      <c r="A21" s="117" t="s">
         <v>85</v>
       </c>
       <c r="B21" s="55"/>
@@ -11265,14 +11265,14 @@
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="99" t="s">
+      <c r="H21" s="68" t="s">
         <v>118</v>
       </c>
       <c r="I21" s="55"/>
-      <c r="J21" s="80"/>
+      <c r="J21" s="69"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="117" t="s">
         <v>87</v>
       </c>
       <c r="B22" s="55"/>
@@ -11283,11 +11283,11 @@
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="99" t="s">
+      <c r="H22" s="68" t="s">
         <v>119</v>
       </c>
       <c r="I22" s="55"/>
-      <c r="J22" s="80"/>
+      <c r="J22" s="69"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="40"/>
@@ -11343,7 +11343,7 @@
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
       <c r="G26" s="19"/>
-      <c r="H26" s="95"/>
+      <c r="H26" s="62"/>
       <c r="I26" s="118"/>
       <c r="J26" s="119"/>
     </row>
@@ -12326,6 +12326,27 @@
     <row r="1003" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="A26:C26"/>
@@ -12336,27 +12357,6 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12375,130 +12375,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="62" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="62" t="s">
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="62" t="s">
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="62" t="s">
+      <c r="P1" s="82"/>
+      <c r="Q1" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="63"/>
-      <c r="S1" s="62" t="s">
+      <c r="R1" s="82"/>
+      <c r="S1" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="98"/>
+      <c r="T1" s="67"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="58"/>
       <c r="C2" s="58"/>
       <c r="D2" s="58"/>
       <c r="E2" s="58"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="64"/>
-      <c r="T2" s="128"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="96"/>
+      <c r="S2" s="95"/>
+      <c r="T2" s="132"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
       <c r="D3" s="58"/>
       <c r="E3" s="58"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="66"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="97"/>
       <c r="H3" s="58"/>
       <c r="I3" s="58"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="66"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="97"/>
       <c r="L3" s="58"/>
       <c r="M3" s="58"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="66"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="66"/>
-      <c r="T3" s="129"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="133"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="68"/>
-      <c r="T4" s="130"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="98"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="134"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="97" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="91"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="91"/>
-      <c r="O5" s="91"/>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="91"/>
-      <c r="R5" s="91"/>
-      <c r="S5" s="91"/>
-      <c r="T5" s="98"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="67"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="102" t="s">
@@ -12509,7 +12509,7 @@
       <c r="D6" s="55"/>
       <c r="E6" s="55"/>
       <c r="F6" s="56"/>
-      <c r="G6" s="99" t="s">
+      <c r="G6" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="55"/>
@@ -12524,7 +12524,7 @@
       <c r="Q6" s="55"/>
       <c r="R6" s="55"/>
       <c r="S6" s="55"/>
-      <c r="T6" s="80"/>
+      <c r="T6" s="69"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="102" t="s">
@@ -12535,7 +12535,7 @@
       <c r="D7" s="55"/>
       <c r="E7" s="55"/>
       <c r="F7" s="56"/>
-      <c r="G7" s="99" t="s">
+      <c r="G7" s="68" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="55"/>
@@ -12550,7 +12550,7 @@
       <c r="Q7" s="55"/>
       <c r="R7" s="55"/>
       <c r="S7" s="55"/>
-      <c r="T7" s="80"/>
+      <c r="T7" s="69"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12753,29 +12753,29 @@
         <v>46</v>
       </c>
       <c r="B15" s="56"/>
-      <c r="C15" s="133" t="s">
+      <c r="C15" s="130" t="s">
         <v>40</v>
       </c>
       <c r="D15" s="56"/>
-      <c r="E15" s="117" t="s">
+      <c r="E15" s="103" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="56"/>
-      <c r="G15" s="117" t="s">
+      <c r="G15" s="103" t="s">
         <v>48</v>
       </c>
       <c r="H15" s="55"/>
       <c r="I15" s="56"/>
-      <c r="J15" s="117" t="s">
+      <c r="J15" s="103" t="s">
         <v>49</v>
       </c>
       <c r="K15" s="56"/>
-      <c r="L15" s="117" t="s">
+      <c r="L15" s="103" t="s">
         <v>50</v>
       </c>
       <c r="M15" s="55"/>
       <c r="N15" s="56"/>
-      <c r="O15" s="117" t="s">
+      <c r="O15" s="103" t="s">
         <v>51</v>
       </c>
       <c r="P15" s="55"/>
@@ -12791,33 +12791,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="131">
+      <c r="A16" s="123">
         <v>1</v>
       </c>
       <c r="B16" s="56"/>
-      <c r="C16" s="132" t="s">
+      <c r="C16" s="124" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="56"/>
-      <c r="E16" s="132" t="s">
+      <c r="E16" s="124" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="56"/>
-      <c r="G16" s="123" t="s">
+      <c r="G16" s="129" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="55"/>
       <c r="I16" s="56"/>
-      <c r="J16" s="123" t="s">
+      <c r="J16" s="129" t="s">
         <v>58</v>
       </c>
       <c r="K16" s="56"/>
-      <c r="L16" s="125" t="s">
+      <c r="L16" s="127" t="s">
         <v>59</v>
       </c>
       <c r="M16" s="55"/>
       <c r="N16" s="56"/>
-      <c r="O16" s="125" t="s">
+      <c r="O16" s="127" t="s">
         <v>60</v>
       </c>
       <c r="P16" s="55"/>
@@ -12833,33 +12833,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="131">
+      <c r="A17" s="123">
         <v>2</v>
       </c>
       <c r="B17" s="56"/>
-      <c r="C17" s="132" t="s">
+      <c r="C17" s="124" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="56"/>
-      <c r="E17" s="132" t="s">
+      <c r="E17" s="124" t="s">
         <v>62</v>
       </c>
       <c r="F17" s="56"/>
-      <c r="G17" s="123" t="s">
+      <c r="G17" s="129" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="55"/>
       <c r="I17" s="56"/>
-      <c r="J17" s="123" t="s">
+      <c r="J17" s="129" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="56"/>
-      <c r="L17" s="125" t="s">
+      <c r="L17" s="127" t="s">
         <v>65</v>
       </c>
       <c r="M17" s="55"/>
       <c r="N17" s="56"/>
-      <c r="O17" s="125" t="s">
+      <c r="O17" s="127" t="s">
         <v>66</v>
       </c>
       <c r="P17" s="55"/>
@@ -12875,21 +12875,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="131"/>
+      <c r="A18" s="123"/>
       <c r="B18" s="56"/>
-      <c r="C18" s="132"/>
+      <c r="C18" s="124"/>
       <c r="D18" s="56"/>
-      <c r="E18" s="132"/>
+      <c r="E18" s="124"/>
       <c r="F18" s="56"/>
-      <c r="G18" s="123"/>
+      <c r="G18" s="129"/>
       <c r="H18" s="55"/>
       <c r="I18" s="56"/>
-      <c r="J18" s="123"/>
+      <c r="J18" s="129"/>
       <c r="K18" s="56"/>
-      <c r="L18" s="125"/>
+      <c r="L18" s="127"/>
       <c r="M18" s="55"/>
       <c r="N18" s="56"/>
-      <c r="O18" s="125"/>
+      <c r="O18" s="127"/>
       <c r="P18" s="55"/>
       <c r="Q18" s="56"/>
       <c r="R18" s="33"/>
@@ -12903,21 +12903,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="131"/>
+      <c r="A19" s="123"/>
       <c r="B19" s="56"/>
-      <c r="C19" s="132"/>
+      <c r="C19" s="124"/>
       <c r="D19" s="56"/>
-      <c r="E19" s="132"/>
+      <c r="E19" s="124"/>
       <c r="F19" s="56"/>
-      <c r="G19" s="123"/>
+      <c r="G19" s="129"/>
       <c r="H19" s="55"/>
       <c r="I19" s="56"/>
-      <c r="J19" s="123"/>
+      <c r="J19" s="129"/>
       <c r="K19" s="56"/>
-      <c r="L19" s="125"/>
+      <c r="L19" s="127"/>
       <c r="M19" s="55"/>
       <c r="N19" s="56"/>
-      <c r="O19" s="125"/>
+      <c r="O19" s="127"/>
       <c r="P19" s="55"/>
       <c r="Q19" s="56"/>
       <c r="R19" s="33"/>
@@ -12931,21 +12931,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="131"/>
+      <c r="A20" s="123"/>
       <c r="B20" s="56"/>
-      <c r="C20" s="132"/>
+      <c r="C20" s="124"/>
       <c r="D20" s="56"/>
-      <c r="E20" s="132"/>
+      <c r="E20" s="124"/>
       <c r="F20" s="56"/>
-      <c r="G20" s="123"/>
+      <c r="G20" s="129"/>
       <c r="H20" s="55"/>
       <c r="I20" s="56"/>
-      <c r="J20" s="123"/>
+      <c r="J20" s="129"/>
       <c r="K20" s="56"/>
-      <c r="L20" s="125"/>
+      <c r="L20" s="127"/>
       <c r="M20" s="55"/>
       <c r="N20" s="56"/>
-      <c r="O20" s="125"/>
+      <c r="O20" s="127"/>
       <c r="P20" s="55"/>
       <c r="Q20" s="56"/>
       <c r="R20" s="33"/>
@@ -12959,21 +12959,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="131"/>
+      <c r="A21" s="123"/>
       <c r="B21" s="56"/>
-      <c r="C21" s="132"/>
+      <c r="C21" s="124"/>
       <c r="D21" s="56"/>
-      <c r="E21" s="132"/>
+      <c r="E21" s="124"/>
       <c r="F21" s="56"/>
-      <c r="G21" s="123"/>
+      <c r="G21" s="129"/>
       <c r="H21" s="55"/>
       <c r="I21" s="56"/>
-      <c r="J21" s="123"/>
+      <c r="J21" s="129"/>
       <c r="K21" s="56"/>
-      <c r="L21" s="125"/>
+      <c r="L21" s="127"/>
       <c r="M21" s="55"/>
       <c r="N21" s="56"/>
-      <c r="O21" s="125"/>
+      <c r="O21" s="127"/>
       <c r="P21" s="55"/>
       <c r="Q21" s="56"/>
       <c r="R21" s="33"/>
@@ -12987,21 +12987,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="131"/>
+      <c r="A22" s="123"/>
       <c r="B22" s="56"/>
-      <c r="C22" s="132"/>
+      <c r="C22" s="124"/>
       <c r="D22" s="56"/>
-      <c r="E22" s="132"/>
+      <c r="E22" s="124"/>
       <c r="F22" s="56"/>
-      <c r="G22" s="123"/>
+      <c r="G22" s="129"/>
       <c r="H22" s="55"/>
       <c r="I22" s="56"/>
-      <c r="J22" s="123"/>
+      <c r="J22" s="129"/>
       <c r="K22" s="56"/>
-      <c r="L22" s="125"/>
+      <c r="L22" s="127"/>
       <c r="M22" s="55"/>
       <c r="N22" s="56"/>
-      <c r="O22" s="125"/>
+      <c r="O22" s="127"/>
       <c r="P22" s="55"/>
       <c r="Q22" s="56"/>
       <c r="R22" s="33"/>
@@ -13015,21 +13015,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="131"/>
+      <c r="A23" s="123"/>
       <c r="B23" s="56"/>
-      <c r="C23" s="132"/>
+      <c r="C23" s="124"/>
       <c r="D23" s="56"/>
-      <c r="E23" s="132"/>
+      <c r="E23" s="124"/>
       <c r="F23" s="56"/>
-      <c r="G23" s="123"/>
+      <c r="G23" s="129"/>
       <c r="H23" s="55"/>
       <c r="I23" s="56"/>
-      <c r="J23" s="123"/>
+      <c r="J23" s="129"/>
       <c r="K23" s="56"/>
-      <c r="L23" s="125"/>
+      <c r="L23" s="127"/>
       <c r="M23" s="55"/>
       <c r="N23" s="56"/>
-      <c r="O23" s="125"/>
+      <c r="O23" s="127"/>
       <c r="P23" s="55"/>
       <c r="Q23" s="56"/>
       <c r="R23" s="33"/>
@@ -13043,21 +13043,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="131"/>
+      <c r="A24" s="123"/>
       <c r="B24" s="56"/>
-      <c r="C24" s="132"/>
+      <c r="C24" s="124"/>
       <c r="D24" s="56"/>
-      <c r="E24" s="132"/>
+      <c r="E24" s="124"/>
       <c r="F24" s="56"/>
-      <c r="G24" s="123"/>
+      <c r="G24" s="129"/>
       <c r="H24" s="55"/>
       <c r="I24" s="56"/>
-      <c r="J24" s="123"/>
+      <c r="J24" s="129"/>
       <c r="K24" s="56"/>
-      <c r="L24" s="125"/>
+      <c r="L24" s="127"/>
       <c r="M24" s="55"/>
       <c r="N24" s="56"/>
-      <c r="O24" s="125"/>
+      <c r="O24" s="127"/>
       <c r="P24" s="55"/>
       <c r="Q24" s="56"/>
       <c r="R24" s="33"/>
@@ -13071,21 +13071,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="131"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="56"/>
-      <c r="C25" s="132"/>
+      <c r="C25" s="124"/>
       <c r="D25" s="56"/>
-      <c r="E25" s="132"/>
+      <c r="E25" s="124"/>
       <c r="F25" s="56"/>
-      <c r="G25" s="123"/>
+      <c r="G25" s="129"/>
       <c r="H25" s="55"/>
       <c r="I25" s="56"/>
-      <c r="J25" s="123"/>
+      <c r="J25" s="129"/>
       <c r="K25" s="56"/>
-      <c r="L25" s="125"/>
+      <c r="L25" s="127"/>
       <c r="M25" s="55"/>
       <c r="N25" s="56"/>
-      <c r="O25" s="125"/>
+      <c r="O25" s="127"/>
       <c r="P25" s="55"/>
       <c r="Q25" s="56"/>
       <c r="R25" s="33"/>
@@ -13099,21 +13099,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="131"/>
+      <c r="A26" s="123"/>
       <c r="B26" s="56"/>
-      <c r="C26" s="132"/>
+      <c r="C26" s="124"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="132"/>
+      <c r="E26" s="124"/>
       <c r="F26" s="56"/>
-      <c r="G26" s="123"/>
+      <c r="G26" s="129"/>
       <c r="H26" s="55"/>
       <c r="I26" s="56"/>
-      <c r="J26" s="123"/>
+      <c r="J26" s="129"/>
       <c r="K26" s="56"/>
-      <c r="L26" s="125"/>
+      <c r="L26" s="127"/>
       <c r="M26" s="55"/>
       <c r="N26" s="56"/>
-      <c r="O26" s="125"/>
+      <c r="O26" s="127"/>
       <c r="P26" s="55"/>
       <c r="Q26" s="56"/>
       <c r="R26" s="33"/>
@@ -13127,21 +13127,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="131"/>
+      <c r="A27" s="123"/>
       <c r="B27" s="56"/>
-      <c r="C27" s="132"/>
+      <c r="C27" s="124"/>
       <c r="D27" s="56"/>
-      <c r="E27" s="132"/>
+      <c r="E27" s="124"/>
       <c r="F27" s="56"/>
-      <c r="G27" s="123"/>
+      <c r="G27" s="129"/>
       <c r="H27" s="55"/>
       <c r="I27" s="56"/>
-      <c r="J27" s="123"/>
+      <c r="J27" s="129"/>
       <c r="K27" s="56"/>
-      <c r="L27" s="125"/>
+      <c r="L27" s="127"/>
       <c r="M27" s="55"/>
       <c r="N27" s="56"/>
-      <c r="O27" s="125"/>
+      <c r="O27" s="127"/>
       <c r="P27" s="55"/>
       <c r="Q27" s="56"/>
       <c r="R27" s="33"/>
@@ -13155,21 +13155,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="131"/>
+      <c r="A28" s="123"/>
       <c r="B28" s="56"/>
-      <c r="C28" s="132"/>
+      <c r="C28" s="124"/>
       <c r="D28" s="56"/>
-      <c r="E28" s="132"/>
+      <c r="E28" s="124"/>
       <c r="F28" s="56"/>
-      <c r="G28" s="123"/>
+      <c r="G28" s="129"/>
       <c r="H28" s="55"/>
       <c r="I28" s="56"/>
-      <c r="J28" s="123"/>
+      <c r="J28" s="129"/>
       <c r="K28" s="56"/>
-      <c r="L28" s="125"/>
+      <c r="L28" s="127"/>
       <c r="M28" s="55"/>
       <c r="N28" s="56"/>
-      <c r="O28" s="125"/>
+      <c r="O28" s="127"/>
       <c r="P28" s="55"/>
       <c r="Q28" s="56"/>
       <c r="R28" s="33"/>
@@ -13183,21 +13183,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="131"/>
+      <c r="A29" s="123"/>
       <c r="B29" s="56"/>
-      <c r="C29" s="132"/>
+      <c r="C29" s="124"/>
       <c r="D29" s="56"/>
-      <c r="E29" s="132"/>
+      <c r="E29" s="124"/>
       <c r="F29" s="56"/>
-      <c r="G29" s="123"/>
+      <c r="G29" s="129"/>
       <c r="H29" s="55"/>
       <c r="I29" s="56"/>
-      <c r="J29" s="123"/>
+      <c r="J29" s="129"/>
       <c r="K29" s="56"/>
-      <c r="L29" s="125"/>
+      <c r="L29" s="127"/>
       <c r="M29" s="55"/>
       <c r="N29" s="56"/>
-      <c r="O29" s="125"/>
+      <c r="O29" s="127"/>
       <c r="P29" s="55"/>
       <c r="Q29" s="56"/>
       <c r="R29" s="33"/>
@@ -13211,21 +13211,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="131"/>
+      <c r="A30" s="123"/>
       <c r="B30" s="56"/>
-      <c r="C30" s="132"/>
+      <c r="C30" s="124"/>
       <c r="D30" s="56"/>
-      <c r="E30" s="132"/>
+      <c r="E30" s="124"/>
       <c r="F30" s="56"/>
-      <c r="G30" s="123"/>
+      <c r="G30" s="129"/>
       <c r="H30" s="55"/>
       <c r="I30" s="56"/>
-      <c r="J30" s="123"/>
+      <c r="J30" s="129"/>
       <c r="K30" s="56"/>
-      <c r="L30" s="125"/>
+      <c r="L30" s="127"/>
       <c r="M30" s="55"/>
       <c r="N30" s="56"/>
-      <c r="O30" s="125"/>
+      <c r="O30" s="127"/>
       <c r="P30" s="55"/>
       <c r="Q30" s="56"/>
       <c r="R30" s="33"/>
@@ -13239,23 +13239,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="134"/>
-      <c r="B31" s="83"/>
-      <c r="C31" s="135"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="135"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="82"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="124"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="126"/>
-      <c r="M31" s="82"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="126"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="83"/>
+      <c r="A31" s="125"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="126"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="135"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="128"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="128"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="72"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14253,6 +14253,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14277,118 +14389,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
